--- a/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 23,62</t>
+          <t>-26,31; 25,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-41,35; 21,57</t>
+          <t>-41,53; 23,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 13,63</t>
+          <t>-62,11; 13,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 53,72</t>
+          <t>-33,96; 50,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,37; 41,62</t>
+          <t>-49,71; 47,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 25,55</t>
+          <t>-89,06; 26,46</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 18,63</t>
+          <t>-3,52; 19,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 16,58</t>
+          <t>-6,77; 17,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 24,88</t>
+          <t>-13,38; 26,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 34,7</t>
+          <t>-4,58; 35,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 34,66</t>
+          <t>-11,55; 34,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 50,03</t>
+          <t>-22,03; 49,96</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 19,17</t>
+          <t>-16,49; 19,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 35,67</t>
+          <t>-6,35; 36,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 19,57</t>
+          <t>-17,9; 18,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 34,01</t>
+          <t>-22,58; 36,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 101,38</t>
+          <t>-9,55; 107,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 42,65</t>
+          <t>-25,87; 41,99</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 14,36</t>
+          <t>-3,93; 12,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 17,0</t>
+          <t>-4,45; 15,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 18,19</t>
+          <t>-12,3; 18,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 25,25</t>
+          <t>-6,04; 22,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 33,29</t>
+          <t>-7,43; 30,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 34,17</t>
+          <t>-20,25; 33,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 25,04</t>
+          <t>-24,64; 24,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 23,3</t>
+          <t>-42,93; 22,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 13,23</t>
+          <t>-71,58; 11,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 50,26</t>
+          <t>-32,2; 51,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 47,54</t>
+          <t>-51,05; 40,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 26,46</t>
+          <t>-88,35; 26,0</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 19,06</t>
+          <t>-3,95; 19,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 17,6</t>
+          <t>-7,02; 17,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 26,72</t>
+          <t>-13,36; 24,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 35,94</t>
+          <t>-6,13; 34,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 34,58</t>
+          <t>-11,4; 35,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 49,96</t>
+          <t>-21,55; 48,09</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 19,89</t>
+          <t>-16,82; 19,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 36,35</t>
+          <t>-5,75; 36,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 18,83</t>
+          <t>-19,15; 17,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 36,29</t>
+          <t>-21,63; 33,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 107,26</t>
+          <t>-10,6; 105,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 41,99</t>
+          <t>-27,22; 35,31</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 12,75</t>
+          <t>-4,01; 14,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,19</t>
+          <t>-3,74; 16,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 18,16</t>
+          <t>-12,88; 17,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 22,05</t>
+          <t>-5,81; 24,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 30,38</t>
+          <t>-6,11; 33,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 33,75</t>
+          <t>-21,41; 34,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-20,8</t>
+          <t>-5,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-37,56%</t>
+          <t>-8,78%</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 24,84</t>
+          <t>-24,59; 23,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 22,65</t>
+          <t>-41,35; 21,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-71,58; 11,66</t>
+          <t>-39,57; 27,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 51,58</t>
+          <t>-34,23; 53,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 40,34</t>
+          <t>-50,37; 41,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-88,35; 26,0</t>
+          <t>-56,26; 66,58</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>-7,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>-13,27%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 19,2</t>
+          <t>-4,24; 18,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 17,01</t>
+          <t>-8,48; 16,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 24,01</t>
+          <t>-19,51; 6,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 34,83</t>
+          <t>-6,43; 34,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 35,7</t>
+          <t>-13,56; 34,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 48,09</t>
+          <t>-30,66; 10,27</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 19,47</t>
+          <t>-16,17; 19,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 36,81</t>
+          <t>-6,19; 35,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 17,38</t>
+          <t>-17,35; 20,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 33,75</t>
+          <t>-21,95; 34,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 105,8</t>
+          <t>-10,31; 101,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 35,31</t>
+          <t>-25,18; 45,39</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,85%</t>
+          <t>-8,36%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 14,34</t>
+          <t>-4,42; 14,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 16,58</t>
+          <t>-3,41; 17,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 17,95</t>
+          <t>-15,53; 5,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 24,75</t>
+          <t>-6,48; 25,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 33,29</t>
+          <t>-5,76; 33,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 34,33</t>
+          <t>-23,62; 9,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-13,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-18,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-8,78%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.936831711644362</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.14073947274277</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6.455945877254438</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.98806620427821</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.04016145851731463</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1631787853820801</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.6879629255239444</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2076988954814755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-24,59; 23,62</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-41,35; 21,57</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-39,57; 27,76</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-34,23; 53,72</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-50,37; 41,62</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-56,26; 66,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-10.28629540174802</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.024156396411094</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.247745831657968</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-14.76762165902773</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3555310179439307</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4407003258050167</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2978834438768028</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.720703556974296</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.76541097255199</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.27352727844019</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>16.66734647004249</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.067485836375289</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.6113446350416607</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.335937051147604</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.927607497319085</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.9260317578701621</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,62</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,98</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-13,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,24; 18,63</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,48; 16,58</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-19,51; 6,25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 34,7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-13,56; 34,66</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-30,66; 10,27</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.017153029876802</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8185110588671705</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9596376379194873</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.460986289918501</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.05534157754548847</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.06612376553810993</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.09863307442933904</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1801126507642167</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.887314509394697</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.788643435390254</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.429048588147694</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.323017369504583</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1441570675486474</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2005822868666207</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2102421764818741</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3975458814193006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-16,17; 19,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 35,67</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-17,35; 20,89</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-21,95; 34,01</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-10,31; 101,38</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-25,18; 45,39</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.219725317363364</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.708032721723629</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.88697419073396</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.540964855153073</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3194936334094116</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.4620845864957611</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4697470649941701</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1348057137328492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-4,98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,36%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-9.345504450864004</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.4769996578608771</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.14863669167391</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.369704074753625</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.41906840187992</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.0308072760768196</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4219990832446275</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.09194448730030627</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 14,36</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,41; 17,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-15,53; 5,23</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-6,48; 25,25</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-5,76; 33,29</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-23,62; 9,71</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.41358834574918</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.00695974302402</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.54851146175507</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.730075364380243</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5934949305660382</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3762125727967604</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1791462003407712</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3228130722958237</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-2.973048690726819</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.174242312241551</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.890831744394033</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.277941006079097</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.1506445008334913</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.536764153633931</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.536173863603055</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.7176106487001191</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.433857554294762</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7210446876788096</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.977215733059039</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.59149110775795</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.07229478137330225</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.05475351622322692</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2166425668212398</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1135250734699942</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.811845747674748</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.197725557893424</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.4410158789971705</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.585055897203741</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2260091593478478</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1453630621009574</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.05084802875635521</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2958005650014883</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.727567300631935</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.815504023735937</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.674636737829599</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.819806716914667</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09362772909261668</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3308258560963747</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.592219890013166</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1418709409786361</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
